--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N116_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N116_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.64955505768258</v>
+        <v>4.33055269687342</v>
       </c>
       <c r="D2" t="n">
-        <v>28.55472703003576</v>
+        <v>4.64014314238081</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.02042269275837</v>
+        <v>2.115818687573235</v>
       </c>
       <c r="D3" t="n">
-        <v>11.16335635546297</v>
+        <v>1.814045407762733</v>
       </c>
       <c r="E3" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.53559289623077</v>
+        <v>5.937033845637501</v>
       </c>
       <c r="D4" t="n">
-        <v>11.62970334961301</v>
+        <v>1.889826794312114</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F4" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.63861315137645</v>
+        <v>6.928774637098674</v>
       </c>
       <c r="D5" t="n">
-        <v>38.39596332949598</v>
+        <v>6.239344041043097</v>
       </c>
       <c r="E5" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.42299561220816</v>
+        <v>4.781236786983826</v>
       </c>
       <c r="D6" t="n">
-        <v>4.466353788748145</v>
+        <v>0.7257824906715735</v>
       </c>
       <c r="E6" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.85078550299419</v>
+        <v>4.850752644236556</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08799638462811</v>
+        <v>5.051799412502067</v>
       </c>
       <c r="E7" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.34773393984839</v>
+        <v>7.369006765225364</v>
       </c>
       <c r="D8" t="n">
-        <v>44.77043623741375</v>
+        <v>7.275195888579735</v>
       </c>
       <c r="E8" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F8" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.39325701717705</v>
+        <v>5.751404265291271</v>
       </c>
       <c r="D9" t="n">
-        <v>35.95652123778407</v>
+        <v>5.842934701139911</v>
       </c>
       <c r="E9" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>7.099747424109739</v>
+        <v>1.153708956417833</v>
       </c>
       <c r="D10" t="n">
-        <v>6.074646647973403</v>
+        <v>0.9871300802956781</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12530230893233</v>
+        <v>4.245361625201503</v>
       </c>
       <c r="D11" t="n">
-        <v>25.83196013403662</v>
+        <v>4.19769352178095</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F11" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.22952944949447</v>
+        <v>4.587298535542851</v>
       </c>
       <c r="D12" t="n">
-        <v>26.33675431233351</v>
+        <v>4.279722575754196</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F12" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.01139026291894</v>
+        <v>5.364350917724328</v>
       </c>
       <c r="D13" t="n">
-        <v>18.33712082089225</v>
+        <v>2.979782133394991</v>
       </c>
       <c r="E13" t="n">
-        <v>10.4678087359799</v>
+        <v>1.701018919596734</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6218837130333</v>
+        <v>2.051056103367912</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
